--- a/distances-communes-gramme.xlsx
+++ b/distances-communes-gramme.xlsx
@@ -583,15 +583,23 @@
           <t>Ans, province de Liège, Belgique</t>
         </is>
       </c>
-      <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="n"/>
+      <c r="G2" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>13</v>
+      </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
           <t>4430, 4431, 4432</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr"/>
-      <c r="K2" s="3" t="inlineStr"/>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>relevé Google Maps 2026-07-30</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -622,11 +630,19 @@
           <t>Awans, province de Liège, Belgique</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n"/>
-      <c r="H3" s="4" t="n"/>
+      <c r="G3" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>13</v>
+      </c>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr"/>
-      <c r="K3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>relevé Google Maps 2026-07-30</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -657,11 +673,19 @@
           <t>Aywaille, province de Liège, Belgique</t>
         </is>
       </c>
-      <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="n"/>
+      <c r="G4" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>36</v>
+      </c>
       <c r="I4" s="3" t="inlineStr"/>
       <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>relevé Google Maps 2026-07-30</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -692,11 +716,19 @@
           <t>Bassenge, province de Liège, Belgique</t>
         </is>
       </c>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
+      <c r="G5" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>relevé Google Maps 2026-07-30</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -727,11 +759,19 @@
           <t>Beyne-Heusay, province de Liège, Belgique</t>
         </is>
       </c>
-      <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="n"/>
+      <c r="G6" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>19</v>
+      </c>
       <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="3" t="inlineStr"/>
-      <c r="K6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>relevé Google Maps 2026-07-30</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -762,11 +802,19 @@
           <t>Blegny, province de Liège, Belgique</t>
         </is>
       </c>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
+      <c r="G7" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>13</v>
+      </c>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr"/>
-      <c r="K7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>relevé Google Maps 2026-07-30</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -797,11 +845,19 @@
           <t>Chaudfontaine, province de Liège, Belgique</t>
         </is>
       </c>
-      <c r="G8" s="4" t="n"/>
-      <c r="H8" s="4" t="n"/>
+      <c r="G8" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>24</v>
+      </c>
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>relevé Google Maps 2026-07-30</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -832,11 +888,19 @@
           <t>Comblain-au-Pont, province de Liège, Belgique</t>
         </is>
       </c>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n"/>
+      <c r="G9" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>42</v>
+      </c>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>relevé Google Maps 2026-07-30</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -867,11 +931,19 @@
           <t>Dalhem, province de Liège, Belgique</t>
         </is>
       </c>
-      <c r="G10" s="4" t="n"/>
-      <c r="H10" s="4" t="n"/>
+      <c r="G10" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>14</v>
+      </c>
       <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="3" t="inlineStr"/>
-      <c r="K10" s="3" t="inlineStr"/>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>relevé Google Maps 2026-07-30</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -902,11 +974,19 @@
           <t>Esneux, province de Liège, Belgique</t>
         </is>
       </c>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="n"/>
+      <c r="G11" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>34</v>
+      </c>
       <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="3" t="inlineStr"/>
-      <c r="K11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>relevé Google Maps 2026-07-30</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -937,11 +1017,19 @@
           <t>Flémalle, province de Liège, Belgique</t>
         </is>
       </c>
-      <c r="G12" s="4" t="n"/>
-      <c r="H12" s="4" t="n"/>
+      <c r="G12" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>22</v>
+      </c>
       <c r="I12" s="3" t="inlineStr"/>
       <c r="J12" s="3" t="inlineStr"/>
-      <c r="K12" s="3" t="inlineStr"/>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>relevé Google Maps 2026-07-30</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -972,11 +1060,19 @@
           <t>Fléron, province de Liège, Belgique</t>
         </is>
       </c>
-      <c r="G13" s="4" t="n"/>
-      <c r="H13" s="4" t="n"/>
+      <c r="G13" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="3" t="inlineStr"/>
-      <c r="K13" s="3" t="inlineStr"/>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>relevé Google Maps 2026-07-30</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1007,11 +1103,19 @@
           <t>Grâce-Hollogne, province de Liège, Belgique</t>
         </is>
       </c>
-      <c r="G14" s="4" t="n"/>
-      <c r="H14" s="4" t="n"/>
+      <c r="G14" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>16</v>
+      </c>
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="3" t="inlineStr"/>
-      <c r="K14" s="3" t="inlineStr"/>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>relevé Google Maps 2026-07-30</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1085,11 +1189,19 @@
           <t>Juprelle, province de Liège, Belgique</t>
         </is>
       </c>
-      <c r="G16" s="4" t="n"/>
-      <c r="H16" s="4" t="n"/>
+      <c r="G16" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="3" t="inlineStr"/>
-      <c r="K16" s="3" t="inlineStr"/>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>relevé Google Maps 2026-07-30</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1120,11 +1232,19 @@
           <t>Liège, province de Liège, Belgique</t>
         </is>
       </c>
-      <c r="G17" s="4" t="n"/>
-      <c r="H17" s="4" t="n"/>
+      <c r="G17" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>18</v>
+      </c>
       <c r="I17" s="3" t="inlineStr"/>
       <c r="J17" s="3" t="inlineStr"/>
-      <c r="K17" s="3" t="inlineStr"/>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>relevé Google Maps 2026-07-30</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1155,11 +1275,19 @@
           <t>Neupré, province de Liège, Belgique</t>
         </is>
       </c>
-      <c r="G18" s="4" t="n"/>
-      <c r="H18" s="4" t="n"/>
+      <c r="G18" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>29</v>
+      </c>
       <c r="I18" s="3" t="inlineStr"/>
       <c r="J18" s="3" t="inlineStr"/>
-      <c r="K18" s="3" t="inlineStr"/>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>relevé Google Maps 2026-07-30</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1190,11 +1318,19 @@
           <t>Oupeye, province de Liège, Belgique</t>
         </is>
       </c>
-      <c r="G19" s="4" t="n"/>
-      <c r="H19" s="4" t="n"/>
+      <c r="G19" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="I19" s="3" t="inlineStr"/>
       <c r="J19" s="3" t="inlineStr"/>
-      <c r="K19" s="3" t="inlineStr"/>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>relevé Google Maps 2026-07-30</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1225,11 +1361,19 @@
           <t>Saint-Nicolas, province de Liège, Belgique</t>
         </is>
       </c>
-      <c r="G20" s="4" t="n"/>
-      <c r="H20" s="4" t="n"/>
+      <c r="G20" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>16</v>
+      </c>
       <c r="I20" s="3" t="inlineStr"/>
       <c r="J20" s="3" t="inlineStr"/>
-      <c r="K20" s="3" t="inlineStr"/>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>relevé Google Maps 2026-07-30</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1311,11 +1455,19 @@
           <t>Soumagne, province de Liège, Belgique</t>
         </is>
       </c>
-      <c r="G22" s="4" t="n"/>
-      <c r="H22" s="4" t="n"/>
+      <c r="G22" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>14</v>
+      </c>
       <c r="I22" s="3" t="inlineStr"/>
       <c r="J22" s="3" t="inlineStr"/>
-      <c r="K22" s="3" t="inlineStr"/>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>relevé Google Maps 2026-07-30</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -1346,11 +1498,19 @@
           <t>Sprimont, province de Liège, Belgique</t>
         </is>
       </c>
-      <c r="G23" s="4" t="n"/>
-      <c r="H23" s="4" t="n"/>
+      <c r="G23" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>32</v>
+      </c>
       <c r="I23" s="3" t="inlineStr"/>
       <c r="J23" s="3" t="inlineStr"/>
-      <c r="K23" s="3" t="inlineStr"/>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>relevé Google Maps 2026-07-30</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -1381,11 +1541,19 @@
           <t>Trooz, province de Liège, Belgique</t>
         </is>
       </c>
-      <c r="G24" s="4" t="n"/>
-      <c r="H24" s="4" t="n"/>
+      <c r="G24" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>26</v>
+      </c>
       <c r="I24" s="3" t="inlineStr"/>
       <c r="J24" s="3" t="inlineStr"/>
-      <c r="K24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>relevé Google Maps 2026-07-30</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -1416,11 +1584,19 @@
           <t>Visé, province de Liège, Belgique</t>
         </is>
       </c>
-      <c r="G25" s="4" t="n"/>
-      <c r="H25" s="4" t="n"/>
+      <c r="G25" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>12</v>
+      </c>
       <c r="I25" s="3" t="inlineStr"/>
       <c r="J25" s="3" t="inlineStr"/>
-      <c r="K25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>relevé Google Maps 2026-07-30</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -1994,7 +2170,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>À REVÉRIFIER dans Maps — OSRM annonce 48 km contre 35 relevés</t>
+          <t>relevé Maps — cohérent avec l'ensemble (60 km/h)</t>
         </is>
       </c>
     </row>
